--- a/ICCE_2AM/online_classes/online_class_attendance_2am.xlsx
+++ b/ICCE_2AM/online_classes/online_class_attendance_2am.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git_projects\asl-rnd\web_programming\ICCE_2AM\online_classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EF3367-F7D6-42F3-99D0-313A2D079B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AD365B-EFC9-488C-A99B-37447EEAD17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{0982E389-66D2-4D88-A1D4-F114AC50152A}"/>
+    <workbookView xWindow="-27885" yWindow="-180" windowWidth="21600" windowHeight="14010" activeTab="1" xr2:uid="{0982E389-66D2-4D88-A1D4-F114AC50152A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -166,9 +166,6 @@
     <t>10-04-2025 (22)</t>
   </si>
   <si>
-    <t>26-10-2025 (19)</t>
-  </si>
-  <si>
     <t>11-09-2025 (27)</t>
   </si>
   <si>
@@ -179,6 +176,9 @@
   </si>
   <si>
     <t>11-07-2025 (28)</t>
+  </si>
+  <si>
+    <t>26-10-2025 (23)</t>
   </si>
 </sst>
 </file>
@@ -186,7 +186,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -296,16 +296,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1187,534 +1187,542 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8" t="s">
+      <c r="B23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8" t="s">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8" t="s">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8" t="s">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8" t="s">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8" t="s">
+      <c r="D26" s="7"/>
+      <c r="E26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8" t="s">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8" t="s">
+      <c r="D27" s="7"/>
+      <c r="E27" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8" t="s">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8" t="s">
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8" t="s">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8" t="s">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7" t="s">
         <v>21</v>
       </c>
     </row>
